--- a/Excel-files/customer_create_1000.xlsx
+++ b/Excel-files/customer_create_1000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS01503\Documents\load testing Script-BSS\Excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A176E4-6EE2-4B45-BCD3-8E38A1BEE337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8705F359-1C63-450F-BA94-5438CEF7A3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="10" windowWidth="19190" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Create" sheetId="1" r:id="rId1"/>
